--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,25 +993,25 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>King, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Business Intelligence Engineer II, Procurement, Real Estate &amp; Facilities Analytics</t>
+          <t>Senior Technical Specialist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>King, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hadoop, Hive, Spark, Scala, Dimensional Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4f8c0cf0c31b9e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Data Engineer</t>
+          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, Hadoop, Snowflake, clustering keys, Oracle, dbt</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebbb3368fcab6386</t>
+          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
+          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NPR</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9334f09070428459</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,59 +2386,59 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Java Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Kafka, Snowflake, Data Modeling, Dimensional Modeling, Kimball, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87b420bcd07d16a3</t>
+          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,104 +2621,104 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer (Go/Typescript)</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Plan A Technologies</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73913eba01c47259</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Back End / Java, Spring Boot, Kafka</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Strongsville, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03649e9af32154c</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>GenAI Python Systems Engineer – Experienced Associate</t>
+          <t>Senior Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PwC</t>
+          <t>Workiva</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Terraform, AWS CloudFormation, Docker, Python</t>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=092180f6fccecac1</t>
+          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Application Security Engineer-68257</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior UX Software Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GRVTY</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, YARN, Scala, SQL Server, MySQL, MongoDB, Docker, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=188385fe594d1176</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,297 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>EagleBank</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer - 1099 Contract</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Bitcot Technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84992a9d853e715d</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solutions Architect (GenAI, Python/Data, AWS)</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, Spark, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794fcf67de18d24f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Backend Java Software Engineer III</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, NoSQL, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46bd797613407be6</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>DevOps / Platform Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Vivacity Tech PBC</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3562,11 +3562,11 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Application Security Engineer-68257</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Application Security Engineer-68257</t>
+          <t>Senior Data &amp; AI Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Workiva</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,505 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Healthcare Analytics Engineer II</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>agilon health</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Engineer 2 - Integrated Merchandising</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Nordstrom</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Data Transformation Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Confie</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Addison, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Lakebase Sales Specialist</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer II</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EagleBank</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Humana</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>KY, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>AI DevOps Engineer - 1099 Contract</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Bitcot Technologies pvt ltd</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hitachi Energy</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
           <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Technical Specialist</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>King, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, API Gateway, IAM</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bf07ec2da4c3701</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,42 +3006,42 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps / Platform Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vivacity Tech PBC</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Cloud Storage, Scala, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d39b7b5a88b4d35</t>
+          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Stylitics</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Platform Engineer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Workiva</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Snowflake, ELT, dbt, Tableau, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094ac7b7f209413b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4240,41 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -3408,17 +3408,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,7 +958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>senior data engineer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6348f1b22dfd1649</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2643,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3632,11 +3632,11 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Application Security Engineer-68257</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4240,6 +4240,41 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Stylitics</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d143b966366bb7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>ML Ops Technical Specialist - DevOps, Python</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
@@ -3611,19 +3611,19 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3632,11 +3632,11 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Data Transformation Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Confie</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4240,41 +4240,6 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visibol</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.4</v>
+        <v>24.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, RDS, Azure, Google Cloud Platform, Scala</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Medallion Architecture, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2462e8855b10b292</t>
+          <t>https://www.indeed.com/viewjob?jk=858aa20205dd4518</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Software Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>24.3</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Medallion Architecture, Scala, Kafka, Snowflake</t>
+          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858aa20205dd4518</t>
+          <t>https://www.indeed.com/viewjob?jk=446f18fd0ddebaff</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Cloud Data Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=446f18fd0ddebaff</t>
+          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer – Baltimore City, MD</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>American Century Investments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, IAM, RDS, Medallion Architecture, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df281f957b19fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Senior Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>Primoris Services Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise / Solution Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Century Investments</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer ( Early Career )-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,59 +1476,59 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,17 +1956,17 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -2503,12 +2503,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -2573,12 +2573,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,59 +3051,59 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,19 +3156,19 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ML Ops Technical Specialist - DevOps, Python</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ECS, Google Cloud Platform, GCP, Cloud Storage, Vertex AI, Kafka, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c14c92fb799da4</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
@@ -3898,17 +3898,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Application Security Engineer-68257</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -4240,6 +4240,41 @@
         </is>
       </c>
       <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Application Security Engineer-68257</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Hitachi Rail</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Masco</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Databricks, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3babca04d3a4353</t>
+          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>American Century Investments</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise / Solution Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Century Investments</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Primoris Services Corporation</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, BigQuery, Hadoop</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14e6d9e0e8ac190f</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer ( Early Career )-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,19 +916,19 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Delta Faucet Company</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Wayzata, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer- Animal Health Nutrition</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Cargill</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -2538,12 +2538,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e29b1ab6a71257</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Concentra DevOps Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Concentra</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, Splunk</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fecf6d8da4c516a0</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Direct Client - Decision Scientist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>The AES Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1974e392d61c948</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,19 +3541,19 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3562,11 +3562,11 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,19 +3646,19 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Transformation Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Confie</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Scala, Snowflake, Dimensional Modeling, ETL, ELT, Airflow, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=049826f47ea60f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Power BI Consultant</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4065,216 +4065,6 @@
         </is>
       </c>
       <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Bitcot Technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Masco</t>
+          <t>American Century Investments</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d37b8249fccee88</t>
+          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Enterprise / Solution Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Century Investments</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Platform &amp; Database Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
+          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Software Developer ( Early Career )-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,52 +1011,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
@@ -1203,25 +1203,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Delta Faucet Company</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, GCP, Cloud Storage, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2a88b7f58cf63d9</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce5e17069dfe6b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer- Animal Health Nutrition</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Spark, Scala, Kafka, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c63dce15e809fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Madison, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Compass</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Aventura, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Modus Closing</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>AI Engineer II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Mitratech</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,59 +2876,59 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Concentra DevOps Engineer II</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Concentra</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Azure, Oracle, SQL Server, MySQL, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=937785ffcf01ce69</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Data Modeler 4D</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Direct Client - Decision Scientist</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The AES Group</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Scala, Oracle, SQL Server, Power BI, Tableau</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,67 +3226,67 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8c04d109704529</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3317,11 +3317,11 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74263f4a52c96ca9</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,29 +3461,29 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Power BI Consultant</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3855,216 +3855,6 @@
         </is>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Bitcot Technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Platform &amp; Database Engineer</t>
+          <t>Software Developer ( Early Career )-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Unity Catalog, Spark, PySpark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28b754997a6cb19c</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Jazwares</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,69 +976,69 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2d4d6b724af8274</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edefefd43be9dc66</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf25f49dcaa3bab</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madison, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be3d62c77468bade</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Compass Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f225032bbf5d84c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Aventura, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,94 +2351,94 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1b07860a5889799</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Modus Closing</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3134c6730945c7c</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,42 +2446,42 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,137 +2596,137 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior SIEM Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>State Street</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Java Backend Engineer (Remote)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Engineer II</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mitratech</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Snowflake, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6fad79af5600169</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, SQS, ECS, RDS, Azure, Kafka, SQL Server, DynamoDB, Data Modeling, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4d13644542e7c9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Healthcare Analytics Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>agilon health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Engineer 2 - Integrated Merchandising</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Modeler 4D</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake, Oracle, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58941ecd857176c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Decision Scientist</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Power BI Consultant</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3505,356 +3505,6 @@
         </is>
       </c>
       <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>EagleBank</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Bitcot Technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Jazwares</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bec398ccd65219f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Patriot Software</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,17 +1326,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>Cleveland Cavaliers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Web Application Architect 3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Bloomberg Industry Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Engineer III - Software</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>PODS</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Clearwater, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,42 +2411,42 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior SIEM Data Engineer</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State Street</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Cloud Storage, Spark, PySpark, Scala, Kafka, Splunk, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41d2133f31f2f069</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
@@ -2673,17 +2673,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>IT Engineer - Cloud Infrastructure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Lead Bank</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Healthcare Analytics Engineer II</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>agilon health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552c2268ad654867</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer 2 - Integrated Merchandising</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14c1f123eec910b1</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Decision Scientist</t>
+          <t>AI DevOps Engineer - 1099 Contract</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bitcot Technologies pvt ltd</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
+          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
+          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Power BI Consultant</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EagleBank</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bitcot Technologies pvt ltd</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Applied AI Engineer II</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3365,146 +3365,6 @@
         </is>
       </c>
       <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise / Solution Architect</t>
+          <t>Software Developer ( Early Career )-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>BMO Financial Group</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, API Gateway, RDS, Azure</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea47f9494f78051</t>
+          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, ECS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fcc3b31ffee88c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Python API Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Patriot Software</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, Kafka, PostgreSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a476aa196196ba0a</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abbott</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, Databricks, Spark, Scala, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e6f4ed087e5ebb6</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cleveland Cavaliers</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, BigQuery, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424fe3c2f51527c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gresham, OR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior Software Engineer - Full Stack</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Sr. Software Engineer - PySpark</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Early Warning Services</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,94 +2071,94 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Web Application Architect 3</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bloomberg Industry Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0251e47fed5cebaa</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Engineer III - Software</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PODS</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Clearwater, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec22207fa44dd71</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Cloud FinOps and AI Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CyberData Technologies Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Java Backend Engineer (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=131c54e2c46fac8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CyberData Technologies Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IT Engineer - Cloud Infrastructure</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lead Bank</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ccc9d2a5b9ebc8e</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Decision Scientist</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Power BI Consultant</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lakebase Sales Specialist</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3015,356 +3015,6 @@
         </is>
       </c>
       <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>EagleBank</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI DevOps Engineer - 1099 Contract</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Bitcot Technologies pvt ltd</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, MLOps, MLflow, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0855620e74f5796e</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Specialist Software Engineering</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, API Gateway, ECS, RDS, Azure, Data Factory, Event Hubs, Zookeeper</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=446f18fd0ddebaff</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Century Investments</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS, RDS</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0b0aed89dff9f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer ( Early Career )-15</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BMO Financial Group</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, NoSQL, CI/CD</t>
+          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae0e52de777b485b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>React Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,19 +706,19 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Angular Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Rust Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Oracle PL/SQL Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Python API Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e17835329bc0a26</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,19 +1126,19 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Blockchain Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f77db4be4ea977d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5be0697da6f5c906</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02208c7a55530f62</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f432e89817efee42</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gresham, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00fc7514d3c7798a</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Earth City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06231d7a635d5a2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Full Stack</t>
+          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, PostgreSQL, MongoDB, Cassandra</t>
+          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=184fc5e6cac22124</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - PySpark</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Early Warning Services</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, PySpark, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=932b9e36940a351b</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d63b50d33467755a</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, SQL Server, MongoDB, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d597f76635493a59</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2490,531 +2490,6 @@
         </is>
       </c>
       <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Children's Hospital Association</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Lenexa, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>COPE Health Solutions</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Cloud FinOps and AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>CyberData Technologies Inc</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Splunk</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3467ce02853b3a0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>EagleBank</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>

--- a/results/job_matches_2026-08-01.xlsx
+++ b/results/job_matches_2026-08-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>24.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Medallion Architecture, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8024a2005fb0b3ea</t>
+          <t>https://www.indeed.com/viewjob?jk=858aa20205dd4518</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.5</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f0ae34753ca05b6</t>
+          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>Fairfax County Government</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfax, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>24.3</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Medallion Architecture, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858aa20205dd4518</t>
+          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java Backend + Angular + AI - Assisted Development)</t>
+          <t>IT-Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cretex Companies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,19 +601,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b87df55d4d491de</t>
+          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Services Engineer SR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Sagent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acba286ebf4d92e</t>
+          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, AI &amp; Salesforce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, Azure, Databricks, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0dc5f06d9c317d2</t>
+          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>React Developer</t>
+          <t>Ops - BigQuery DBA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,102 +706,102 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33f0eb65140bf8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Angular Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Azure, Google Cloud Platform, YARN, Scala, Kafka, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffdaf62c5e2b9c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analyst III</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fairfax County Government</t>
+          <t>First American</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fairfax, VA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, BigQuery, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb89d5ea5a1962dc</t>
+          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rust Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cae36a5a408f0114</t>
+          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle PL/SQL Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1b93b7b128e21c2</t>
+          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IT-Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cretex Companies</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7be6dab7ca375291</t>
+          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Services Engineer SR</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sagent</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acf1657228e472b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32917ee5dd7a2f21</t>
+          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, AI &amp; Salesforce</t>
+          <t>data engineer sr- ST; Seattle, WA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, Data Modeling, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed75d3affdec047</t>
+          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ops - BigQuery DBA</t>
+          <t>Senior Power BI Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AFL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Duncan, SC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Scala, Snowflake, Snowflake Schema, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,137 +1021,137 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1a0846ae4c043fb</t>
+          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78da46a020c5c9a9</t>
+          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First American</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=296becbd334bbc67</t>
+          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Architect, Audience Lifecycle</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>National Public Radio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a8605190a502c1</t>
+          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>CLERA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02ddfaa0f7254c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Operations Data Engineering Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Southern Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e46d6854a6af634a</t>
+          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>ioT engineer senior, Seattle WA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,137 +1231,137 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8deff62964f62f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+          <t>Senior Engineer, Big Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FCT</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=faf74f07ae6081d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>data engineer sr- ST; Seattle, WA</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, MapReduce, YARN, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=520c25a2261458b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Bethpage, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, dbt, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e13bc402f1e5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Power BI Developer</t>
+          <t>Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AFL</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Duncan, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20e18aa5f93b2f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Spark, Scala, Kafka, Snowflake, Oracle, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60b180c3277b0ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Cloud Platform &amp; Infrastructure</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CloudZero</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef5e1ba1d628d749</t>
+          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Audience Lifecycle</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>National Public Radio</t>
+          <t>Nextlink Internet</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, GCP, Spark, Scala, Snowflake, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=947d58877f957a3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ioT engineer senior, Seattle WA</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Starbucks</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, MySQL, Splunk, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f4f2dbe0b92bd99</t>
+          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Launch Automation Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLERA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40184011356fb182</t>
+          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Operations Data Engineering Analyst</t>
+          <t>Senior Knowledge Graph Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Southern Company</t>
+          <t>United Airlines</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db6c6c4982aba82</t>
+          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer, Big Data</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Children's Hospital Association</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lenexa, KS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Google Cloud Platform, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cd92d13a4a4bb35</t>
+          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Blockchain Developer</t>
+          <t>DevOps / Platform Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>COPE Health Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,102 +1651,102 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bf64c9316192e39</t>
+          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Lakebase Sales Specialist</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c85fe3d6b042982b</t>
+          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Development Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>EagleBank</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethpage, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36f3b49aebbbfcfd</t>
+          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d6b18534a1abc5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efa15317bf1d4a7e</t>
+          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Step Functions, SQS, RDS, Azure, GCP, Kafka, Splunk, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,137 +1826,137 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7befa886e8e2b3a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Infra, AI for Drug Discovery</t>
+          <t>Decision Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, IAM, Scala, MLOps, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a5de50052388b80</t>
+          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Power BI Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nextlink Internet</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, SQL Server, MongoDB, NoSQL, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a4f40f85cfe5737</t>
+          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Launch Automation Engineer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bf3991a8b55df54</t>
+          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Knowledge Graph Developer</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, ELT, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2478b1194a745a56</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Applied AI Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Vertex AI, Spark, PySpark, Scala, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea2c5e32ab039b3c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Children's Hospital Association</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Spark, Scala, Spark Streaming, Kafka, ETL, ELT, DataOps</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f175efe5aa839f13</t>
+          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DevOps / Platform Infrastructure Engineer</t>
+          <t>Application Security Engineer-68257</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>COPE Health Solutions</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Azure, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2070,426 +2070,6 @@
         </is>
       </c>
       <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6097dde62dadd0a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Lakebase Sales Specialist</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MySQL, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a6b31b12af4777d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>EagleBank</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Spark, PySpark, Scala, Snowflake, CI/CD</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6fe61838cc3330dd</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>TN, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e714098ae5cec8b</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68067a30d3435be3</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>KY, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, PostgreSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2f86a70b2dfc7a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Decision Scientist</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Data Lake Storage, Oracle, SQL Server, Power BI, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=059945040a6a3e85</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Power BI Consultant</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Fractal Analytics</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Data Modeling</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eadb4ecc87b42f52</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=113a02d9c51c0bff</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Morristown, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd5b2f1603e18a4</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Applied AI Engineer II</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLflow, SonarQube, Git</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ff48c95fd7d75a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Hitachi Energy</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5d29cf07978c240b</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Application Security Engineer-68257</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Hitachi Rail</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes, Jenkins, SonarQube</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5259d199d57d6f49</t>
         </is>
